--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.51152284413213</v>
+        <v>7.558122462171472</v>
       </c>
       <c r="D2" t="n">
-        <v>45.28622096354812</v>
+        <v>7.359010906576571</v>
       </c>
       <c r="E2" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F2" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.91606453727537</v>
+        <v>7.786360487307249</v>
       </c>
       <c r="D3" t="n">
-        <v>46.83376078055345</v>
+        <v>7.610486126839937</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F3" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.74851562764339</v>
+        <v>7.10913378949205</v>
       </c>
       <c r="D4" t="n">
-        <v>42.49543928660331</v>
+        <v>6.905508884073038</v>
       </c>
       <c r="E4" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F4" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.79993558336056</v>
+        <v>4.354989532296091</v>
       </c>
       <c r="D5" t="n">
-        <v>25.5750362313967</v>
+        <v>4.155943387601964</v>
       </c>
       <c r="E5" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F5" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.13190254988472</v>
+        <v>6.846434164356268</v>
       </c>
       <c r="D6" t="n">
-        <v>41.55861825084775</v>
+        <v>6.753275465762759</v>
       </c>
       <c r="E6" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F6" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.17898108085401</v>
+        <v>7.666584425638777</v>
       </c>
       <c r="D7" t="n">
-        <v>46.93736326919389</v>
+        <v>7.627321531244007</v>
       </c>
       <c r="E7" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F7" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.29521830420687</v>
+        <v>2.647972974433616</v>
       </c>
       <c r="D8" t="n">
-        <v>15.11621645783097</v>
+        <v>2.456385174397533</v>
       </c>
       <c r="E8" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F8" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.56537098808052</v>
+        <v>7.241872785563084</v>
       </c>
       <c r="D9" t="n">
-        <v>44.62935105793467</v>
+        <v>7.252269546914384</v>
       </c>
       <c r="E9" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F9" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.510788886256949</v>
+        <v>1.058003194016754</v>
       </c>
       <c r="D10" t="n">
-        <v>5.347479137243361</v>
+        <v>0.8689653598020463</v>
       </c>
       <c r="E10" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F10" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.11074014574023</v>
+        <v>3.917995273682787</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63260459619295</v>
+        <v>3.840298246881354</v>
       </c>
       <c r="E11" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F11" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.38293812002697</v>
+        <v>4.287227444504383</v>
       </c>
       <c r="D12" t="n">
-        <v>20.85854865576696</v>
+        <v>3.389514156562132</v>
       </c>
       <c r="E12" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F12" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.60739061652238</v>
+        <v>7.411200975184887</v>
       </c>
       <c r="D13" t="n">
-        <v>45.99229480800295</v>
+        <v>7.473747906300479</v>
       </c>
       <c r="E13" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F13" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.74720022696057</v>
+        <v>3.533920036881093</v>
       </c>
       <c r="D14" t="n">
-        <v>21.96511975274844</v>
+        <v>3.569331959821621</v>
       </c>
       <c r="E14" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F14" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.49001811607756</v>
+        <v>1.867127943862604</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8101197778214</v>
+        <v>1.269144463895977</v>
       </c>
       <c r="E15" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F15" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.34385025534254</v>
+        <v>2.655875666493162</v>
       </c>
       <c r="D16" t="n">
-        <v>17.5641680702503</v>
+        <v>2.854177311415673</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F16" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.63296303988754</v>
+        <v>4.165356493981726</v>
       </c>
       <c r="D17" t="n">
-        <v>26.65401782719325</v>
+        <v>4.331277896918904</v>
       </c>
       <c r="E17" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F17" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25.58913794662884</v>
+        <v>4.158234916327187</v>
       </c>
       <c r="D18" t="n">
-        <v>26.73013280924732</v>
+        <v>4.343646581502689</v>
       </c>
       <c r="E18" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F18" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>35.73969361845551</v>
+        <v>5.807700212999021</v>
       </c>
       <c r="D19" t="n">
-        <v>36.66401535266073</v>
+        <v>5.957902494807368</v>
       </c>
       <c r="E19" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F19" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>30.76892676250887</v>
+        <v>4.999950598907691</v>
       </c>
       <c r="D20" t="n">
-        <v>31.4654139420732</v>
+        <v>5.113129765586895</v>
       </c>
       <c r="E20" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F20" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>33.56391036996052</v>
+        <v>5.454135435118586</v>
       </c>
       <c r="D21" t="n">
-        <v>34.62556973387337</v>
+        <v>5.626655081754423</v>
       </c>
       <c r="E21" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F21" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>42.85539468501214</v>
+        <v>6.964001636314474</v>
       </c>
       <c r="D22" t="n">
-        <v>43.8436727113106</v>
+        <v>7.124596815587974</v>
       </c>
       <c r="E22" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F22" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>24.97992418584523</v>
+        <v>4.059237680199851</v>
       </c>
       <c r="D23" t="n">
-        <v>26.22432946961968</v>
+        <v>4.261453538813198</v>
       </c>
       <c r="E23" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F23" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>37.56592421367977</v>
+        <v>6.104462684722963</v>
       </c>
       <c r="D24" t="n">
-        <v>28.38469155755259</v>
+        <v>4.612512378102297</v>
       </c>
       <c r="E24" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F24" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>39.19425003889106</v>
+        <v>6.369065631319796</v>
       </c>
       <c r="D25" t="n">
-        <v>36.73437085141992</v>
+        <v>5.969335263355738</v>
       </c>
       <c r="E25" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F25" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>24.83403382680935</v>
+        <v>4.03553049685652</v>
       </c>
       <c r="D26" t="n">
-        <v>21.8365580212969</v>
+        <v>3.548440678460747</v>
       </c>
       <c r="E26" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F26" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>13.57009835795026</v>
+        <v>2.205140983166918</v>
       </c>
       <c r="D27" t="n">
-        <v>10.80363825527305</v>
+        <v>1.755591216481871</v>
       </c>
       <c r="E27" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F27" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>29.7508508281696</v>
+        <v>4.834513259577561</v>
       </c>
       <c r="D28" t="n">
-        <v>29.67427220621298</v>
+        <v>4.822069233509609</v>
       </c>
       <c r="E28" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F28" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>13.71175128712143</v>
+        <v>2.228159584157232</v>
       </c>
       <c r="D29" t="n">
-        <v>12.6502367377431</v>
+        <v>2.055663469883254</v>
       </c>
       <c r="E29" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F29" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>20.80819212281942</v>
+        <v>3.381331219958156</v>
       </c>
       <c r="D30" t="n">
-        <v>7.808663528218974</v>
+        <v>1.268907823335583</v>
       </c>
       <c r="E30" t="n">
-        <v>11.94582690958907</v>
+        <v>1.941196872808225</v>
       </c>
       <c r="F30" t="n">
-        <v>12.80186818910266</v>
+        <v>2.080303580729183</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
